--- a/大會師總戰報_20260615/🎨_全策略大會師總表_20260615.xlsx
+++ b/大會師總戰報_20260615/🎨_全策略大會師總表_20260615.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,43 +478,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4721.TWO</t>
+          <t>1342.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>美琪瑪</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>117.5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="F2" t="n">
-        <v>4665</v>
+        <v>2096</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3093.TWO</t>
+          <t>1307.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64.7</v>
+        <v>36.75</v>
       </c>
       <c r="E3" t="n">
         <v>2.2</v>
       </c>
       <c r="F3" t="n">
-        <v>3458</v>
+        <v>2834</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -540,12 +540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4976.TW</t>
+          <t>1434.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.6</v>
+        <v>16.65</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>2917</v>
+        <v>2237</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -571,12 +571,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6166.TW</t>
+          <t>1808.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>潤隆</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>141</v>
+        <v>31.9</v>
       </c>
       <c r="E5" t="n">
         <v>1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>3680</v>
+        <v>3072</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -602,12 +602,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6788.TWO</t>
+          <t>2393.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>449</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2077</v>
+        <v>5528</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -633,291 +633,291 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3450.TW</t>
+          <t>2204.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>中華</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>56.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="F7" t="n">
-        <v>5448</v>
+        <v>1855</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2903.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>960</v>
+        <v>23.85</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>16532</v>
+        <v>4753</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>2887.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4470</v>
+        <v>30.2</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="F9" t="n">
-        <v>11647</v>
+        <v>157208</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9933.TW</t>
+          <t>6196.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>42.8</v>
+        <v>548</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F10" t="n">
-        <v>8074</v>
+        <v>3889</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5392.TWO</t>
+          <t>6409.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44.9</v>
+        <v>930</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="n">
-        <v>6957</v>
+        <v>1519</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3149.TW</t>
+          <t>6153.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>正達</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>87.40000000000001</v>
+        <v>22.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="n">
-        <v>4165</v>
+        <v>28567</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3289.TWO</t>
+          <t>8105.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宜特</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 老余裸K_賺賠比精選</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>169</v>
+        <v>22.45</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="F13" t="n">
-        <v>1947</v>
+        <v>41248</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3413.TW</t>
+          <t>3322.TWO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 四均線起漲精選</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>322</v>
+        <v>15.35</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F14" t="n">
-        <v>4562</v>
+        <v>2628</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5426.TWO</t>
+          <t>2851.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>中再保</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35.6</v>
+        <v>37.15</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F15" t="n">
-        <v>3009</v>
+        <v>1902</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6548.TWO</t>
+          <t>1608.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>華榮</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>91.8</v>
+        <v>34.4</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="n">
-        <v>2846</v>
+        <v>5673</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -943,27 +943,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6191.TW</t>
+          <t>1708.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>東鹼</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 四均線起漲精選</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="F17" t="n">
-        <v>21329</v>
+        <v>11596</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -974,12 +974,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2405.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>輔信</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.45</v>
+        <v>18.9</v>
       </c>
       <c r="E18" t="n">
         <v>1.1</v>
       </c>
       <c r="F18" t="n">
-        <v>4285</v>
+        <v>57479</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1005,12 +1005,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1563.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1147</v>
+        <v>8916</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1036,27 +1036,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3234.TWO</t>
+          <t>2536.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>宏普</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>122.5</v>
+        <v>21.95</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>2834</v>
+        <v>1466</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1067,27 +1067,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3311.TW</t>
+          <t>5469.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲基礎版 | 老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41.3</v>
+        <v>83.7</v>
       </c>
       <c r="E21" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="F21" t="n">
-        <v>3901</v>
+        <v>3015</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1098,213 +1098,213 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>6139.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61.6</v>
+        <v>805</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F22" t="n">
-        <v>31476</v>
+        <v>5499</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>5864.TWO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>致和證</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>105.25</v>
+        <v>47.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="F23" t="n">
-        <v>100138</v>
+        <v>8930</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1569.TWO</t>
+          <t>6585.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49.85</v>
+        <v>136</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F24" t="n">
-        <v>942</v>
+        <v>1892</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1809.TW</t>
+          <t>2641.TWO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中釉</t>
+          <t>正德</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51.5</v>
+        <v>18.8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F25" t="n">
-        <v>6650</v>
+        <v>2913</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1301.TW</t>
+          <t>2323.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47.25</v>
+        <v>11.2</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F26" t="n">
-        <v>36123</v>
+        <v>9946</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0055.TW</t>
+          <t>2302.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>元大MSCI金融</t>
+          <t>麗正</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>34.65</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F27" t="n">
-        <v>967</v>
+        <v>1715</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2316.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>171.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5669</v>
+        <v>43895</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1315,12 +1315,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>1709.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>和益</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>940</v>
+        <v>21.35</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>42057</v>
+        <v>1697</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2375</v>
+        <v>25.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F30" t="n">
-        <v>27846</v>
+        <v>7735</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>1326.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55.7</v>
+        <v>48.8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>6442</v>
+        <v>21643</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1408,12 +1408,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>1313.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>159</v>
+        <v>11.25</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>27698</v>
+        <v>4214</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -1439,27 +1439,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>53.9</v>
+        <v>105.25</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="n">
-        <v>10131</v>
+        <v>95906</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>2457.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>飛宏</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>141.5</v>
+        <v>30.1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F34" t="n">
-        <v>328524</v>
+        <v>9031</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1501,12 +1501,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1319.TW</t>
+          <t>2439.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>105</v>
+        <v>92.3</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="F35" t="n">
-        <v>5358</v>
+        <v>5573</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1532,27 +1532,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>2427.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>三商電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>26</v>
+        <v>22.65</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F36" t="n">
-        <v>4392</v>
+        <v>808</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1563,12 +1563,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3049.TW</t>
+          <t>2413.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>精金</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.75</v>
+        <v>61.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11301</v>
+        <v>23193</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1594,12 +1594,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3044.TW</t>
+          <t>2352.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳世達</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>520</v>
+        <v>31</v>
       </c>
       <c r="E38" t="n">
         <v>0.9</v>
       </c>
       <c r="F38" t="n">
-        <v>3476</v>
+        <v>8353</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1625,12 +1625,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3041.TW</t>
+          <t>2034.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>揚智</t>
+          <t>允強</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>20.25</v>
       </c>
       <c r="E39" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F39" t="n">
-        <v>5627</v>
+        <v>2586</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1656,12 +1656,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2206.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>202</v>
+        <v>63</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="F40" t="n">
-        <v>13702</v>
+        <v>1993</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3031.TW</t>
+          <t>2208.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>佰鴻</t>
+          <t>台船</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28.75</v>
+        <v>17.9</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>705</v>
+        <v>2674</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1718,12 +1718,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3023.TW</t>
+          <t>2010.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>春源</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>319</v>
+        <v>24.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="F42" t="n">
-        <v>974</v>
+        <v>2756</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1749,12 +1749,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3019.TW</t>
+          <t>2030.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>彰源</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1763,13 +1763,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>158</v>
+        <v>18.45</v>
       </c>
       <c r="E43" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F43" t="n">
-        <v>16716</v>
+        <v>1317</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -1780,27 +1780,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2441.TW</t>
+          <t>1301.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>127</v>
+        <v>45.25</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>9334</v>
+        <v>21404</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -1811,27 +1811,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3008.TW</t>
+          <t>1584.TWO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>精剛</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4420</v>
+        <v>19.65</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>3671</v>
+        <v>689</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1842,27 +1842,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2630.TW</t>
+          <t>1612.TW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>宏泰</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>39.35</v>
+        <v>37.7</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F46" t="n">
-        <v>867</v>
+        <v>1126</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2465.TW</t>
+          <t>1609.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>麗臺</t>
+          <t>大亞</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>83</v>
+        <v>37.3</v>
       </c>
       <c r="E47" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="F47" t="n">
-        <v>2315</v>
+        <v>5918</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -1904,27 +1904,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2419.TW</t>
+          <t>2812.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>仲琦</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.75</v>
+        <v>19.5</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F48" t="n">
-        <v>2227</v>
+        <v>13150</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -1935,12 +1935,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2428.TW</t>
+          <t>2615.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F49" t="n">
-        <v>3339</v>
+        <v>12769</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -1966,27 +1966,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2369.TW</t>
+          <t>3152.TWO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>菱生</t>
+          <t>璟德</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>35.75</v>
+        <v>221</v>
       </c>
       <c r="E50" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F50" t="n">
-        <v>14276</v>
+        <v>4213</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2375.TW</t>
+          <t>3060.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>凱美</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>189.5</v>
+        <v>31.15</v>
       </c>
       <c r="E51" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="F51" t="n">
-        <v>13541</v>
+        <v>2824</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -2028,27 +2028,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>3264.TWO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4815</v>
+        <v>227.5</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="F52" t="n">
-        <v>1251</v>
+        <v>9120</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -2059,12 +2059,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>51.4</v>
+        <v>418</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F53" t="n">
-        <v>99517</v>
+        <v>4953</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -2090,27 +2090,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3543.TW</t>
+          <t>3665.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32.55</v>
+        <v>2310</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F54" t="n">
-        <v>506</v>
+        <v>3902</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -2121,27 +2121,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3504.TW</t>
+          <t>4114.TWO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>82.09999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>2329</v>
+        <v>848</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -2152,12 +2152,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3653.TW</t>
+          <t>4532.TW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>瑞智</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3835</v>
+        <v>24.45</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1450</v>
+        <v>1074</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -2183,27 +2183,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3689.TWO</t>
+          <t>3576.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>119.5</v>
+        <v>19.8</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="F57" t="n">
-        <v>1928</v>
+        <v>74101</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -2214,12 +2214,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3704.TW</t>
+          <t>4534.TWO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>慶騰</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>47.7</v>
+        <v>33</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F58" t="n">
-        <v>4367</v>
+        <v>3651</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -2245,12 +2245,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3596.TW</t>
+          <t>2646.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>190.5</v>
+        <v>20.6</v>
       </c>
       <c r="E59" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1922</v>
+        <v>5954</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -2276,12 +2276,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3294.TWO</t>
+          <t>2634.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>39.4</v>
+        <v>47.15</v>
       </c>
       <c r="E60" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F60" t="n">
-        <v>2387</v>
+        <v>5663</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -2307,12 +2307,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>2885.TW</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>423</v>
+        <v>63.9</v>
       </c>
       <c r="E61" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F61" t="n">
-        <v>16518</v>
+        <v>23090</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -2338,27 +2338,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>2905.TW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>三商</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2335</v>
+        <v>14.9</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="F62" t="n">
-        <v>2066</v>
+        <v>1859</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
@@ -2369,27 +2369,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3321.TW</t>
+          <t>3014.TW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>同泰</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>22.45</v>
+        <v>153</v>
       </c>
       <c r="E63" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="F63" t="n">
-        <v>1826</v>
+        <v>4591</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -2400,12 +2400,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3357.TWO</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>322</v>
+        <v>20.4</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F64" t="n">
-        <v>14140</v>
+        <v>79066</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
@@ -2431,27 +2431,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3339.TWO</t>
+          <t>2601.TW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>45</v>
+        <v>5.75</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F65" t="n">
-        <v>3604</v>
+        <v>1788</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -2462,27 +2462,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3362.TWO</t>
+          <t>5452.TWO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>176.5</v>
+        <v>32.2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>6954</v>
+        <v>1532</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
@@ -2493,12 +2493,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3114.TWO</t>
+          <t>5351.TWO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>好德</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>43.45</v>
+        <v>88.7</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>960</v>
+        <v>27894</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -2524,12 +2524,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>5009.TWO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>榮剛</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>590</v>
+        <v>36.3</v>
       </c>
       <c r="E68" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F68" t="n">
-        <v>50819</v>
+        <v>2692</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4952.TW</t>
+          <t>4939.TWO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>亞電</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>58.5</v>
+        <v>66.2</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="F69" t="n">
-        <v>4834</v>
+        <v>12882</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -2586,27 +2586,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>4714.TWO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>252</v>
+        <v>13.55</v>
       </c>
       <c r="E70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>10452</v>
+        <v>680</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -2617,12 +2617,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4919.TW</t>
+          <t>4763.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>193</v>
+        <v>44.45</v>
       </c>
       <c r="E71" t="n">
         <v>0.6</v>
       </c>
       <c r="F71" t="n">
-        <v>7848</v>
+        <v>4867</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -2648,12 +2648,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4760.TWO</t>
+          <t>4542.TWO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>401.5</v>
+        <v>335.5</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="F72" t="n">
-        <v>1606</v>
+        <v>472</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -2679,27 +2679,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4577.TWO</t>
+          <t>5701.TWO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>劍湖山</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>91</v>
+        <v>4.93</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F73" t="n">
-        <v>753</v>
+        <v>869</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
@@ -2710,12 +2710,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3717.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯嘉投控</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>22.25</v>
+        <v>15.6</v>
       </c>
       <c r="E74" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F74" t="n">
-        <v>3470</v>
+        <v>21254</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3707.TWO</t>
+          <t>6026.TWO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>漢磊</t>
+          <t>福邦證</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>81.7</v>
+        <v>17.25</v>
       </c>
       <c r="E75" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F75" t="n">
-        <v>14868</v>
+        <v>4364</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
@@ -2772,12 +2772,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6187.TWO</t>
+          <t>5876.TW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1130</v>
+        <v>42.5</v>
       </c>
       <c r="E76" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F76" t="n">
-        <v>3124</v>
+        <v>8352</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
@@ -2803,12 +2803,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6155.TW</t>
+          <t>6209.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2817,13 +2817,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>90.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E77" t="n">
         <v>0.6</v>
       </c>
       <c r="F77" t="n">
-        <v>18774</v>
+        <v>13703</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
@@ -2834,12 +2834,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6220.TWO</t>
+          <t>6214.TW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>37</v>
+        <v>145.5</v>
       </c>
       <c r="E78" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>2683</v>
+        <v>2251</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
@@ -2865,27 +2865,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6207.TWO</t>
+          <t>6257.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>136</v>
+        <v>221.5</v>
       </c>
       <c r="E79" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F79" t="n">
-        <v>7618</v>
+        <v>8987</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
@@ -2896,12 +2896,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6259.TWO</t>
+          <t>5536.TWO</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>30.35</v>
+        <v>1180</v>
       </c>
       <c r="E80" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>2909</v>
+        <v>1105</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -2927,12 +2927,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6426.TW</t>
+          <t>5521.TW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>209</v>
+        <v>10.55</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1295</v>
+        <v>7184</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
@@ -2958,12 +2958,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>6505.TW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2972,13 +2972,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1920</v>
+        <v>52.8</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F82" t="n">
-        <v>3767</v>
+        <v>5681</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -2989,12 +2989,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4973.TWO</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>210</v>
+        <v>72.3</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F83" t="n">
-        <v>3151</v>
+        <v>8094</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
@@ -3020,27 +3020,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6588.TWO</t>
+          <t>6693.TWO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F84" t="n">
-        <v>504</v>
+        <v>1977</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -3051,27 +3051,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6584.TWO</t>
+          <t>6691.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>四均線起漲精選</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>625</v>
+        <v>689</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="F85" t="n">
-        <v>593</v>
+        <v>2580</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -3082,27 +3082,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6683.TWO</t>
+          <t>7780.TW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1585</v>
+        <v>18.8</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F86" t="n">
-        <v>1453</v>
+        <v>3013</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -3113,12 +3113,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6643.TWO</t>
+          <t>8011.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>493</v>
+        <v>18.3</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>511</v>
+        <v>1164</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
@@ -3144,27 +3144,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6719.TW</t>
+          <t>8033.TW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>240.5</v>
+        <v>129.5</v>
       </c>
       <c r="E88" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1480</v>
+        <v>1700</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -3175,27 +3175,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6770.TW</t>
+          <t>6919.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E89" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>86191</v>
+        <v>2813</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
@@ -3206,27 +3206,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6862.TW</t>
+          <t>8088.TWO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>202</v>
+        <v>61.4</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="F90" t="n">
-        <v>1786</v>
+        <v>4121</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
@@ -3237,27 +3237,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6668.TW</t>
+          <t>8213.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>39.85</v>
+        <v>36.05</v>
       </c>
       <c r="E91" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>1742</v>
+        <v>709</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -3268,27 +3268,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6909.TW</t>
+          <t>8261.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>47.65</v>
+        <v>173.5</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="F92" t="n">
-        <v>713</v>
+        <v>13685</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -3299,27 +3299,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6919.TW</t>
+          <t>8932.TWO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>95.5</v>
+        <v>106.5</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="F93" t="n">
-        <v>4329</v>
+        <v>11173</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -3330,12 +3330,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>8935.TWO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>邦泰</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3344,13 +3344,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>30.55</v>
+        <v>21.9</v>
       </c>
       <c r="E94" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="F94" t="n">
-        <v>8979</v>
+        <v>432</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -3361,12 +3361,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8110.TW</t>
+          <t>9904.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>57.5</v>
+        <v>26.65</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F95" t="n">
-        <v>11322</v>
+        <v>17817</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
@@ -3392,27 +3392,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8255.TWO</t>
+          <t>9940.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>183</v>
+        <v>19.75</v>
       </c>
       <c r="E96" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="F96" t="n">
-        <v>4232</v>
+        <v>986</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>9945.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3437,79 +3437,17 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>624</v>
+        <v>26.8</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F97" t="n">
-        <v>1908</v>
+        <v>14890</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>8936.TWO</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>國統</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>回後買上漲基礎版</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F98" t="n">
-        <v>14159</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>8996.TW</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>回後買上漲基礎版</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1255</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1445</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="n">
         <v>1</v>
       </c>
     </row>
